--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1154,8 +1154,12 @@
           <t>CW18</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>19145.79</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14617.11</v>
+      </c>
       <c r="E19" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1166,7 +1170,9 @@
         <v>3878230</v>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>2406.08</v>
+      </c>
       <c r="J19" t="n">
         <v>35</v>
       </c>
@@ -2396,7 +2402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,211 +2420,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>260085-780B Auto Spray</t>
+          <t>260065-P708 upper wrapping tool</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19779.33871121</v>
+        <v>34560.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>260050-Click Rim方向盘热压包覆</t>
+          <t>250383-F2N DAB门盖包覆胎模</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3718.306</v>
+        <v>4924.9849098</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>250379-长滑轨自动装配线</t>
+          <t>260109-DAB自动包覆&amp;EPW展示</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2734.05538434</v>
+        <v>4024.84817</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260109-DAB自动包覆&amp;EPW展示</t>
+          <t>260127-E2LB-2 IP小件热压胎模</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2148.25</v>
+        <v>3123.853979</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>250383-F2N DAB门盖包覆胎模</t>
+          <t>240283-赛力斯 F3 CNSL F3 1800包边机</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1928.14</v>
+        <v>2406.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>250262-W530 IP CUN  welding tool</t>
+          <t>260130-四转台锡焊设备</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1627.535868</v>
+        <v>1582.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>250188-MX11-9门盖包覆胎模A</t>
+          <t>250157-F1L 遮阳板5合1装配线</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1387.597219</v>
+        <v>1151.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>250362-MX增量灯头线</t>
+          <t>260129-金桥E2LB-2-IP自动挂架</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>569</v>
+        <v>816.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>260115-X90DP双组分喷胶设备 第二台</t>
+          <t>260050-Click Rim方向盘热压包覆</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>425.06778033</v>
+        <v>562.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>240231-L234 RHD Top Skin Pre-Fix tooling</t>
+          <t>260053-V530 地图袋包边模具后门</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>387.7109877</v>
+        <v>424.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>260116-X90DP双组分喷胶设备 第一台</t>
+          <t>260031-F05&amp;F03 DP产品共用-上料机构+移栽抓手及胎具</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>367.18233106</v>
+        <v>252.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>260082-F2N灯头模组自动装配线</t>
+          <t>260116-X90DP双组分喷胶设备 第一台</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>309.02</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>240255-灯头线一期装配检测线</t>
+          <t>260115-X90DP双组分喷胶设备 第二台</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>309.02</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>250301-小米昆仑自动线</t>
+          <t>250372-北京V530 焊接模具OP2&amp;换模车</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>309.02</v>
+        <v>105.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>260053-V530 地图袋包边模具后门</t>
+          <t>260101-合肥辊胶设备+防错</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>271.2</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>260052-V530 地图袋包边模具前门</t>
+          <t>250379-长滑轨自动装配线</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>243.79</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>260065-P708 upper wrapping tool</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>226.56</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>250372-北京V530 焊接模具OP2&amp;换模车</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>187.9824</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>260102-标准1200小压机备机</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>144.4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>260079-780 Flaming Process</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>14.08</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>240291-Ncar灯头线X6治具抓手</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1.28</v>
+        <v>6.09</v>
       </c>
     </row>
   </sheetData>
@@ -2632,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2650,191 +2606,171 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>金宇隆</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10111.61848664</v>
+        <v>34560.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>王一飞</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9890.222419499998</v>
+        <v>5558.007058800001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>陈帅</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3876.5551878</v>
+        <v>4733.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>齐永安</t>
+          <t>陆怡沩</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3718.306</v>
+        <v>4525.396</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>张俣健</t>
+          <t>陆定豪</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2148.25</v>
+        <v>2406.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>陈帅</t>
+          <t>樊爱强</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1928.14</v>
+        <v>1782.51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>徐义星</t>
+          <t>韦少官</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1808.8312</v>
+        <v>1582.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>程德宝</t>
+          <t>潘翼伟</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>733.13</v>
+        <v>1151.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>陈佳荣</t>
+          <t>王晓宇</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>618.04</v>
+        <v>816.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>陈雨杭</t>
+          <t>周华盛</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>387.7109877</v>
+        <v>562.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>樊皆杰</t>
+          <t>王俊聪</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>328.5</v>
+        <v>424.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>郝秀霞</t>
+          <t>陈冉</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>309.02</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>郭新杰</t>
+          <t>齐永安</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>272.48</v>
+        <v>252.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>高一恒</t>
+          <t>陆昱</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>243.79</v>
+        <v>105.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>刘东林</t>
+          <t>黄蒙</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>227</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>金宇隆</t>
+          <t>赵鹏</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>226.56</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>丁宝强</t>
+          <t>王万芳</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>144.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>徐迪</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>陆昱</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>43.9824</v>
+        <v>6.09</v>
       </c>
     </row>
   </sheetData>
@@ -2848,7 +2784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2863,6 +2799,16 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>240071-VW426 DP welding machine</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2406.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -2588,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2626,150 +2626,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>陈帅</t>
+          <t>樊爱强</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4733.17</v>
+        <v>1782.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>陆怡沩</t>
+          <t>韦少官</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4525.396</v>
+        <v>1582.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>陆定豪</t>
+          <t>王晓宇</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2406.08</v>
+        <v>816.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>樊爱强</t>
+          <t>周华盛</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1782.51</v>
+        <v>562.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>韦少官</t>
+          <t>陈冉</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1582.12</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>潘翼伟</t>
+          <t>黄蒙</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1151.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>王晓宇</t>
+          <t>赵鹏</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>816.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>周华盛</t>
+          <t>王万芳</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>562.9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>王俊聪</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>424.78</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>陈冉</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>齐永安</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>252.31</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>陆昱</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>105.84</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>黄蒙</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>赵鹏</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>65.7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>王万芳</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
         <v>6.09</v>
       </c>
     </row>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1192,8 +1192,12 @@
           <t>CW19</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>32515.61</v>
+      </c>
+      <c r="D20" t="n">
+        <v>61607.24</v>
+      </c>
       <c r="E20" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1204,7 +1208,9 @@
         <v>3954373</v>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>23073.89</v>
+      </c>
       <c r="J20" t="n">
         <v>34</v>
       </c>
@@ -2402,7 +2408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2420,71 +2426,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>260065-P708 upper wrapping tool</t>
+          <t>240235-V540 IP US Welding Machine</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34560.83</v>
+        <v>6985.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250383-F2N DAB门盖包覆胎模</t>
+          <t>250347-WS FRA line update</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4924.9849098</v>
+        <v>6125.603008</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260109-DAB自动包覆&amp;EPW展示</t>
+          <t>250379-长滑轨自动装配线</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4024.84817</v>
+        <v>5553.20238074</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260127-E2LB-2 IP小件热压胎模</t>
+          <t>260065-P708 upper wrapping tool</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3123.853979</v>
+        <v>4566.41931034</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>240283-赛力斯 F3 CNSL F3 1800包边机</t>
+          <t>260072-2026年亚太备件采购</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2406.08</v>
+        <v>4088.498</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>260130-四转台锡焊设备</t>
+          <t>260128-E2LB-2 IP上盖板热压胎模</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1582.12</v>
+        <v>3200.3218349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>250157-F1L 遮阳板5合1装配线</t>
+          <t>250383-F2N DAB门盖包覆胎模</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1151.2</v>
+        <v>2937.34</v>
       </c>
     </row>
     <row r="9">
@@ -2494,87 +2500,157 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>816.5</v>
+        <v>2878.9328572</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>260050-Click Rim方向盘热压包覆</t>
+          <t>250275-W530 IP CUN lamination tool</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>562.9</v>
+        <v>2479.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>260053-V530 地图袋包边模具后门</t>
+          <t>260042-426 PAB chute cell CI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>424.78</v>
+        <v>1972.564675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>260031-F05&amp;F03 DP产品共用-上料机构+移栽抓手及胎具</t>
+          <t>250055-</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>252.31</v>
+        <v>1671.238416</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>260116-X90DP双组分喷胶设备 第一台</t>
+          <t>260052-V530 地图袋包边模具前门</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>128</v>
+        <v>1080.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>260115-X90DP双组分喷胶设备 第二台</t>
+          <t>240255-灯头线一期装配检测线</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>128</v>
+        <v>713.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>250372-北京V530 焊接模具OP2&amp;换模车</t>
+          <t>260127-E2LB-2 IP小件热压胎模</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>105.84</v>
+        <v>580.3525731999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>260101-合肥辊胶设备+防错</t>
+          <t>260135-四转台锡焊设备</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>65.7</v>
+        <v>574.1368</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>250379-长滑轨自动装配线</t>
+          <t>250109-Ford U625 Lamination D (Rear)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6.09</v>
+        <v>339.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>250362-MX增量灯头线</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>299.18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>250372-北京V530 焊接模具OP2&amp;换模车</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>150.96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>260077-P780 2050 单工位压机</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>95.23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>260109-DAB自动包覆&amp;EPW展示</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>95.23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>260115-X90DP双组分喷胶设备 第二台</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>260116-X90DP双组分喷胶设备 第一台</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>250278-F2N遮阳板五合一设备</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>14.8</v>
       </c>
     </row>
   </sheetData>
@@ -2588,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2606,101 +2682,191 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>金宇隆</t>
+          <t>王翔</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34560.83</v>
+        <v>6125.603008</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>张智浩</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5558.007058800001</v>
+        <v>4088.498</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>樊爱强</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1782.51</v>
+        <v>3758.85020484</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>韦少官</t>
+          <t>古亮</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1582.12</v>
+        <v>2897.83931034</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>王晓宇</t>
+          <t>黄定辉</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>816.5</v>
+        <v>2731.575</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>周华盛</t>
+          <t>丁宝强</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>562.9</v>
+        <v>2421.79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>陈冉</t>
+          <t>岳孟飞</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>256</v>
+        <v>1972.564675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>黄蒙</t>
+          <t>樊皆杰</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>1879.32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>赵鹏</t>
+          <t>金宇隆</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65.7</v>
+        <v>1668.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>徐天丰</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1394.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>阚城奔</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1110.44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>高一恒</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>780.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>樊爱强</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>338.29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>胡超</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>王万芳</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>6.09</v>
+      <c r="B16" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>程德宝</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>101.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>黄琳健</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>95.23</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>陈志彬</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>韦少官</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>30.23</v>
       </c>
     </row>
   </sheetData>
@@ -2714,7 +2880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2732,11 +2898,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>240071-VW426 DP welding machine</t>
+          <t>250264-EU V530 IP CUN welding tool OP2-LHD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2406.08</v>
+        <v>8097.04</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>250338-EHV DP 自动包覆胎具（后右热压）</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6938.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>250262-EU V530 IP CUN welding tool</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5055.37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>250373-北京V530 焊接模具CUN&amp;换模车</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1668.58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>250212-T6 DAB门盖包覆胎模</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1314.7</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -2664,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,61 +2682,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>王翔</t>
+          <t>陆定豪</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6125.603008</v>
+        <v>6985.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>张智浩</t>
+          <t>王翔</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4088.498</v>
+        <v>6125.603008</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>陆怡沩</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3758.85020484</v>
+        <v>4958.596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>古亮</t>
+          <t>张智浩</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2897.83931034</v>
+        <v>4088.498</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>黄定辉</t>
+          <t>陈帅</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2731.575</v>
+        <v>3949.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>丁宝强</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2421.79</v>
+        <v>3758.85020484</v>
       </c>
     </row>
     <row r="8">
@@ -2762,51 +2762,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>金宇隆</t>
+          <t>刘东林</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1668.58</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>徐天丰</t>
+          <t>张俣健</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1394.95</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>阚城奔</t>
+          <t>唐兆丰</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1110.44</v>
+        <v>543.9068000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>高一恒</t>
+          <t>王俊聪</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>780.8</v>
+        <v>457.1428572</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>樊爱强</t>
+          <t>廖诗禄</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>338.29</v>
+        <v>339.6</v>
       </c>
     </row>
     <row r="15">
@@ -2822,51 +2822,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>王万芳</t>
+          <t>陆昱</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>115</v>
+        <v>150.96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>程德宝</t>
+          <t>齐永安</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>101.6</v>
+        <v>95.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>黄琳健</t>
+          <t>王中兴</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>95.23</v>
+        <v>87.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>陈志彬</t>
+          <t>潘翼伟</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>50.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>韦少官</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>30.23</v>
+        <v>14.8</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -2664,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,181 +2682,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>陆定豪</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6985.52</v>
+        <v>3758.85020484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>王翔</t>
+          <t>古亮</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6125.603008</v>
+        <v>2897.83931034</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>陆怡沩</t>
+          <t>黄定辉</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4958.596</v>
+        <v>2731.575</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>张智浩</t>
+          <t>丁宝强</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4088.498</v>
+        <v>2421.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>陈帅</t>
+          <t>岳孟飞</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3949.82</v>
+        <v>1972.564675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>金宇隆</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3758.85020484</v>
+        <v>1668.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>岳孟飞</t>
+          <t>徐天丰</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1972.564675</v>
+        <v>1394.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>樊皆杰</t>
+          <t>阚城奔</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1879.32</v>
+        <v>1110.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>刘东林</t>
+          <t>高一恒</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1418</v>
+        <v>780.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>张俣健</t>
+          <t>樊爱强</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>600</v>
+        <v>338.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>唐兆丰</t>
+          <t>胡超</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>543.9068000000001</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>王俊聪</t>
+          <t>王万芳</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>457.1428572</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>廖诗禄</t>
+          <t>程德宝</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>339.6</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>胡超</t>
+          <t>黄琳健</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>300</v>
+        <v>95.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>陆昱</t>
+          <t>陈志彬</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>150.96</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>齐永安</t>
+          <t>韦少官</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95.23</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>王中兴</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>87.81</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>潘翼伟</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>14.8</v>
+        <v>30.23</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -2868,7 +2868,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>250264-EU V530 IP CUN welding tool OP2-LHD</t>
+          <t>250264-Mercedes-Benz,EU V530-IP, welding</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2878,7 +2878,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250338-EHV DP 自动包覆胎具（后右热压）</t>
+          <t>250338-Huawei Anhui,EHV-DP,Lamination</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2888,7 +2888,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>250262-EU V530 IP CUN welding tool</t>
+          <t>250262-Mercedes-Benz,EU V530-IP welding,250262</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2908,7 +2908,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>250212-T6 DAB门盖包覆胎模</t>
+          <t>250212-Tes,T6-DAB, Lamination</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -2868,7 +2868,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>250264-Mercedes-Benz,EU V530-IP, welding</t>
+          <t>250264-EU V530 IP CUN welding tool OP2-LHD</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2878,7 +2878,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250338-Huawei Anhui,EHV-DP,Lamination</t>
+          <t>250338-EHV DP 自动包覆胎具（后右热压）</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2888,7 +2888,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>250262-Mercedes-Benz,EU V530-IP welding,250262</t>
+          <t>250262-EU V530 IP CUN welding tool</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2908,7 +2908,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>250212-Tes,T6-DAB, Lamination</t>
+          <t>250212-T6 DAB门盖包覆胎模</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -2526,7 +2526,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>250055-</t>
+          <t>250055-BMW,G68 LCI-IP,US Welding</t>
         </is>
       </c>
       <c r="B12" t="n">

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1230,8 +1230,12 @@
           <t>CW20</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>14804.53</v>
+      </c>
+      <c r="D21" t="n">
+        <v>26297.7</v>
+      </c>
       <c r="E21" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1242,7 +1246,9 @@
         <v>4036404</v>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>21672.27</v>
+      </c>
       <c r="J21" t="n">
         <v>33</v>
       </c>
@@ -2408,7 +2414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2426,131 +2432,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>240235-V540 IP US Welding Machine</t>
+          <t>260128-E2LB-2 IP上盖板热压胎模</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6985.52</v>
+        <v>16307.8063433</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250347-WS FRA line update</t>
+          <t>250188-MX11-9门盖包覆胎模A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6125.603008</v>
+        <v>3074.798862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>250379-长滑轨自动装配线</t>
+          <t>260138-E68 DP1200小压机</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5553.20238074</v>
+        <v>2858.9062832</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260065-P708 upper wrapping tool</t>
+          <t>250347-WS FRA line update</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4566.41931034</v>
+        <v>2523.956163</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>260072-2026年亚太备件采购</t>
+          <t>260052-V530 地图袋包边模具前门</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4088.498</v>
+        <v>2101.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>260128-E2LB-2 IP上盖板热压胎模</t>
+          <t>260129-金桥E2LB-2-IP自动挂架</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3200.3218349</v>
+        <v>2083.706222598</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>250383-F2N DAB门盖包覆胎模</t>
+          <t>260053-V530 地图袋包边模具后门</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2937.34</v>
+        <v>1954.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>260129-金桥E2LB-2-IP自动挂架</t>
+          <t>250275-W530 IP CUN lamination tool</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2878.9328572</v>
+        <v>1509.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>250275-W530 IP CUN lamination tool</t>
+          <t>250379-长滑轨自动装配线</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2479.32</v>
+        <v>996.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>260042-426 PAB chute cell CI</t>
+          <t>230211-BR223 DP FOST Press and edge-folding tool</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1972.564675</v>
+        <v>699.23395</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>250055-BMW,G68 LCI-IP,US Welding</t>
+          <t>260042-426 PAB chute cell CI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1671.238416</v>
+        <v>662.1400000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>260052-V530 地图袋包边模具前门</t>
+          <t>260130-四转台锡焊设备</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1080.8</v>
+        <v>554.3788</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>240255-灯头线一期装配检测线</t>
+          <t>260135-四转台锡焊设备</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>713.3</v>
+        <v>449.38</v>
       </c>
     </row>
     <row r="15">
@@ -2560,97 +2566,67 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>580.3525731999999</v>
+        <v>351.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>260135-四转台锡焊设备</t>
+          <t>250301-小米昆仑自动线</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>574.1368</v>
+        <v>319.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>250109-Ford U625 Lamination D (Rear)</t>
+          <t>260093-水性辊胶设备+EOL视觉检测（K321&amp;P166）第一台</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>339.6</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>250362-MX增量灯头线</t>
+          <t>250187-MX11门盖包覆设备A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>299.18</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>250372-北京V530 焊接模具OP2&amp;换模车</t>
+          <t>260085-780B Auto Spray</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>150.96</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>260077-P780 2050 单工位压机</t>
+          <t>260017-F2N10lm抓手治具</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>95.23</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>260109-DAB自动包覆&amp;EPW展示</t>
+          <t>250059-F2水胶片材辊胶机设备</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>95.23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>260115-X90DP双组分喷胶设备 第二台</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>260116-X90DP双组分喷胶设备 第一台</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>250278-F2N遮阳板五合一设备</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>14.8</v>
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>
@@ -2664,7 +2640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,91 +2658,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>阚成奔</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3758.85020484</v>
+        <v>13480.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>古亮</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2897.83931034</v>
+        <v>7190.541287728</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>黄定辉</t>
+          <t>黄琳健</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2731.575</v>
+        <v>2210.2862832</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>丁宝强</t>
+          <t>王晓宇</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2421.79</v>
+        <v>1999.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>岳孟飞</t>
+          <t>黄东方</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1972.564675</v>
+        <v>1509.86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>金宇隆</t>
+          <t>张雷</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1668.58</v>
+        <v>996.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>徐天丰</t>
+          <t>丁宝强</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1394.95</v>
+        <v>648.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>阚城奔</t>
+          <t>周理文</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1110.44</v>
+        <v>449.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>高一恒</t>
+          <t>黄定辉</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>780.8</v>
+        <v>432.81025317</v>
       </c>
     </row>
     <row r="11">
@@ -2776,67 +2752,77 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>338.29</v>
+        <v>351.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>胡超</t>
+          <t>邢舟</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>300</v>
+        <v>221.26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>王万芳</t>
+          <t>赵鹏</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>115</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>程德宝</t>
+          <t>胡超</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>101.6</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>黄琳健</t>
+          <t>韦少官</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95.23</v>
+        <v>30.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>陈志彬</t>
+          <t>王一飞</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>韦少官</t>
+          <t>徐义星</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.23</v>
+        <v>14.21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>付根平</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>
@@ -2850,7 +2836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2868,51 +2854,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>250264-EU V530 IP CUN welding tool OP2-LHD</t>
+          <t>250262-EU V530 IP CUN welding tool</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8097.04</v>
+        <v>9756.799999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250338-EHV DP 自动包覆胎具（后右热压）</t>
+          <t>240071-VW426 DP welding machine</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6938.2</v>
+        <v>4420.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>250262-EU V530 IP CUN welding tool</t>
+          <t>250338-EHV DP 自动包覆胎具（后右热压）</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5055.37</v>
+        <v>2654.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>250373-北京V530 焊接模具CUN&amp;换模车</t>
+          <t>250340-EHV DP 自动包覆胎具（后右冷压）</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1668.58</v>
+        <v>1268.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>250212-T6 DAB门盖包覆胎模</t>
+          <t>250373-北京V530 焊接模具CUN&amp;换模车</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1314.7</v>
+        <v>893.41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>240129-Tesla Everest Suede Topper Scoring Alignmnt machine</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>250055-G68 LCI IP 设备改造（沈阳）</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>508.98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>250301-小米昆仑自动线</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>452.21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>250145-F1L CNSL装配线+EOL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>412.81</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>250362-MX增量灯头线</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>220.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>250367-EHY PL超声波焊接设备（第二台）</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>140.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>240256-JH-C灯头模组生产线</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>79.5</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1268,8 +1268,12 @@
           <t>CW21</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>20010.88</v>
+      </c>
+      <c r="D22" t="n">
+        <v>60406.8</v>
+      </c>
       <c r="E22" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1280,7 +1284,9 @@
         <v>4213133</v>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
       <c r="J22" t="n">
         <v>32</v>
       </c>
@@ -2414,7 +2420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2432,201 +2438,181 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>260128-E2LB-2 IP上盖板热压胎模</t>
+          <t>260133-X90模架改压机 第二台</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16307.8063433</v>
+        <v>28936.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250188-MX11-9门盖包覆胎模A</t>
+          <t>250201-M0301 双机器人转台焊机</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3074.798862</v>
+        <v>17529.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260138-E68 DP1200小压机</t>
+          <t>250379-长滑轨自动装配线</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2858.9062832</v>
+        <v>10901.4382858</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>250347-WS FRA line update</t>
+          <t>260109-DAB自动包覆&amp;EPW展示</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2523.956163</v>
+        <v>6349.05406</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>260052-V530 地图袋包边模具前门</t>
+          <t>260085-780B Auto Spray</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2101.26</v>
+        <v>4420.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>260129-金桥E2LB-2-IP自动挂架</t>
+          <t>260065-P708 upper wrapping tool</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2083.706222598</v>
+        <v>2829.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>260053-V530 地图袋包边模具后门</t>
+          <t>240184-V540 DP 喷胶热压模具（后左一副）</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1954.17</v>
+        <v>1826.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>250275-W530 IP CUN lamination tool</t>
+          <t>260036-F05 CNSL 装配线体改造（T0402 CNSL线搬迁）</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1509.86</v>
+        <v>1734.496524</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>250379-长滑轨自动装配线</t>
+          <t>250379--</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>996.02</v>
+        <v>864</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>230211-BR223 DP FOST Press and edge-folding tool</t>
+          <t>250103-G58热压包覆1模2胎具outer（EPW）</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>699.23395</v>
+        <v>823</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>260042-426 PAB chute cell CI</t>
+          <t>250279-F2N遮阳板五合一胎具</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>662.1400000000001</v>
+        <v>459.3354913</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>260130-四转台锡焊设备</t>
+          <t>260082-F2N灯头模组自动装配线</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>554.3788</v>
+        <v>445.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>260135-四转台锡焊设备</t>
+          <t>260053-V530 地图袋包边模具后门</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>449.38</v>
+        <v>262.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>260127-E2LB-2 IP小件热压胎模</t>
+          <t>250355-SHB 仪表板下本体总成卡扣自动装配设备</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>351.02</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>250301-小米昆仑自动线</t>
+          <t>260063-WL Conveyor</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>319.66</v>
+        <v>204.0696</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>260093-水性辊胶设备+EOL视觉检测（K321&amp;P166）第一台</t>
+          <t>250308-G66 side bolster DV lamination tool</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>159</v>
+        <v>134.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>250187-MX11门盖包覆设备A</t>
+          <t>260031-F05&amp;F03 DP产品共用-上料机构+移栽抓手及胎具</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.36</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>260085-780B Auto Spray</t>
+          <t>250188-MX11-9门盖包覆胎模A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>260017-F2N10lm抓手治具</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>14.21</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>250059-F2水胶片材辊胶机设备</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3.25</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2640,7 +2626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2658,11 +2644,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>阚成奔</t>
+          <t>徐义星</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13480.17</v>
+        <v>9769.524000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2672,157 +2658,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7190.541287728</v>
+        <v>6165.897075299999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>黄琳健</t>
+          <t>王一飞</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2210.2862832</v>
+        <v>4420.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>王晓宇</t>
+          <t>金宇龙</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1999.09</v>
+        <v>2829.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>黄东方</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1509.86</v>
+        <v>877.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>张雷</t>
+          <t>阚城奔</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>996.02</v>
+        <v>824.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>丁宝强</t>
+          <t>金宇隆</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>648.62</v>
+        <v>344.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>周理文</t>
+          <t>张雷</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>449.38</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>黄定辉</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>432.81025317</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>樊爱强</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>351.02</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>邢舟</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>221.26</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>赵鹏</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>62.38</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>胡超</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>51.36</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>韦少官</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>30.93</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>王一飞</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>徐义星</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>14.21</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>付根平</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3.25</v>
+        <v>35.2</v>
       </c>
     </row>
   </sheetData>
@@ -2836,7 +2732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2851,126 +2747,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>250262-EU V530 IP CUN welding tool</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>9756.799999999999</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>240071-VW426 DP welding machine</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4420.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>250338-EHV DP 自动包覆胎具（后右热压）</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2654.28</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>250340-EHV DP 自动包覆胎具（后右冷压）</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1268.68</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>250373-北京V530 焊接模具CUN&amp;换模车</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>893.41</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>240129-Tesla Everest Suede Topper Scoring Alignmnt machine</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>250055-G68 LCI IP 设备改造（沈阳）</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>508.98</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>250301-小米昆仑自动线</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>452.21</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>250145-F1L CNSL装配线+EOL</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>412.81</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>250362-MX增量灯头线</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>220.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>250367-EHY PL超声波焊接设备（第二台）</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>140.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>240256-JH-C灯头模组生产线</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>79.5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -2518,7 +2518,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>250379--</t>
+          <t>250379-</t>
         </is>
       </c>
       <c r="B10" t="n">

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="dfXM_ZJ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="dfRM_ZJ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="dfTK_ZJ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfXM_ZJ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfRM_ZJ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfTK_ZJ" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -2458,7 +2458,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>250379-长滑轨自动装配线</t>
+          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2518,7 +2518,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>250379-</t>
+          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
         </is>
       </c>
       <c r="B10" t="n">

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfXM_ZJ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfRM_ZJ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfTK_ZJ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="dfXM_ZJ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="dfRM_ZJ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="dfTK_ZJ" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1306,8 +1306,12 @@
           <t>CW22</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>11587.77</v>
+      </c>
+      <c r="D23" t="n">
+        <v>31869.85</v>
+      </c>
       <c r="E23" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1318,7 +1322,9 @@
         <v>4325267</v>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
       <c r="J23" t="n">
         <v>31</v>
       </c>
@@ -2420,7 +2426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2438,181 +2444,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>260133-X90模架改压机 第二台</t>
+          <t>260132-X90模架改压机 第一台</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28936.55</v>
+        <v>14273.258</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250201-M0301 双机器人转台焊机</t>
+          <t>260043-2026年南非Rosslyn备件2（Serbia)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17529.69</v>
+        <v>7149.6758621</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
+          <t>260053-V530 地图袋包边模具后门</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10901.4382858</v>
+        <v>5743.559999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260109-DAB自动包覆&amp;EPW展示</t>
+          <t>230187-NCAR 超声焊机-设备</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6349.05406</v>
+        <v>3313.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>260085-780B Auto Spray</t>
+          <t>250371-北京V530 焊接模具OP1&amp;换模车</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4420.8</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>260065-P708 upper wrapping tool</t>
+          <t>260085-780B Auto Spray</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2829.76</v>
+        <v>2481.200976</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>240184-V540 DP 喷胶热压模具（后左一副）</t>
+          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1826.1</v>
+        <v>1527.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>260036-F05 CNSL 装配线体改造（T0402 CNSL线搬迁）</t>
+          <t>260063-WL Conveyor</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1734.496524</v>
+        <v>600.7060329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
+          <t>250187-MX11门盖包覆设备A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>864</v>
+        <v>389.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>250103-G58热压包覆1模2胎具outer（EPW）</t>
+          <t>260129-金桥E2LB-2-IP自动挂架</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>823</v>
+        <v>279.8527373</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>250279-F2N遮阳板五合一胎具</t>
+          <t>260050-Click Rim方向盘热压包覆</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>459.3354913</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>260082-F2N灯头模组自动装配线</t>
+          <t>240291-Ncar灯头线X6治具抓手</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>445.2</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>260053-V530 地图袋包边模具后门</t>
+          <t>230179-BR223 DP Armrest Press Lamination Machine</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>262.76</v>
+        <v>31.96915163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>250355-SHB 仪表板下本体总成卡扣自动装配设备</t>
+          <t>260082-F2N灯头模组自动装配线</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>260063-WL Conveyor</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>204.0696</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>250308-G66 side bolster DV lamination tool</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>134.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>260031-F05&amp;F03 DP产品共用-上料机构+移栽抓手及胎具</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>250188-MX11-9门盖包覆胎模A</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>42</v>
+        <v>9.75</v>
       </c>
     </row>
   </sheetData>
@@ -2626,7 +2592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2644,81 +2610,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>徐义星</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9769.524000000001</v>
+        <v>229135.466094949</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>苏楠</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6165.897075299999</v>
+        <v>14273.258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>王一飞</t>
+          <t>郭新杰</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4420.8</v>
+        <v>5777.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>金宇龙</t>
+          <t>王晓宇</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2829.76</v>
+        <v>1436.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>黄琳健</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>877.1</v>
+        <v>389.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>阚城奔</t>
+          <t>古亮</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>824.66</v>
+        <v>141.5746</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>金宇隆</t>
+          <t>张振</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>344.1</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>张雷</t>
+          <t>周华盛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.2</v>
+        <v>38.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>罗浩</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>32.5</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1344,8 +1344,12 @@
           <t>CW23</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>10108.42</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35218.34</v>
+      </c>
       <c r="E24" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1356,7 +1360,9 @@
         <v>4444705</v>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
       <c r="J24" t="n">
         <v>30</v>
       </c>
@@ -2426,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,141 +2450,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>260132-X90模架改压机 第一台</t>
+          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14273.258</v>
+        <v>8996.5508224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>260043-2026年南非Rosslyn备件2（Serbia)</t>
+          <t>250367-EHY 双机器人焊接设备 第二台</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7149.6758621</v>
+        <v>4630.221467</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260053-V530 地图袋包边模具后门</t>
+          <t>260044-DF-Liuzhou,F05-CNSL,Lamination</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5743.559999999999</v>
+        <v>2640.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>230187-NCAR 超声焊机-设备</t>
+          <t>260117-Papa工厂E4备件</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3313.64</v>
+        <v>2344.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>250371-北京V530 焊接模具OP1&amp;换模车</t>
+          <t>240245-MBEAM 520 UBL Glue spray machine</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>260085-780B Auto Spray</t>
+          <t>250293-MMA Clipping machine</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2481.200976</v>
+        <v>1142.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
+          <t>260065-P708 upper wrapping tool</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1527.2</v>
+        <v>1055.232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>260063-WL Conveyor</t>
+          <t>260050-Click Rim方向盘热压包覆</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>600.7060329</v>
+        <v>730.0884956</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>250187-MX11门盖包覆设备A</t>
+          <t>260085-780B Auto Spray</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>389.1</v>
+        <v>337.4344828</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>260129-金桥E2LB-2-IP自动挂架</t>
+          <t>260079-780 Flaming Process</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>279.8527373</v>
+        <v>235.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>260050-Click Rim方向盘热压包覆</t>
+          <t>260116-X90DP双组分喷胶设备 第一台</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.7</v>
+        <v>57.54447293</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>240291-Ncar灯头线X6治具抓手</t>
+          <t>260135-smartmi,KUNLUN-light,welding.260135.M</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.42</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>230179-BR223 DP Armrest Press Lamination Machine</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>31.96915163</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>260082-F2N灯头模组自动装配线</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>9.75</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -2592,7 +2578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2610,91 +2596,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>高一恒</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>229135.466094949</v>
+        <v>15948.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>苏楠</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14273.258</v>
+        <v>11933.47212733</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>郭新杰</t>
+          <t>刘璟华</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5777.98</v>
+        <v>5394.349376</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>王晓宇</t>
+          <t>徐义星</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1436.9</v>
+        <v>4804.4688</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>黄琳健</t>
+          <t>王万芳</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>389.1</v>
+        <v>3685.80531</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>古亮</t>
+          <t>陈志彬</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>141.5746</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>张振</t>
+          <t>长江</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>109.6</v>
+        <v>1142.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>周华盛</t>
+          <t>王晓宇,王万芳</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.7</v>
+        <v>196.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>罗浩</t>
+          <t>郝秀霞</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.5</v>
+        <v>195.67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>唐明明</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1382,8 +1382,12 @@
           <t>CW24</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>19077.96</v>
+      </c>
+      <c r="D25" t="n">
+        <v>35640.93</v>
+      </c>
       <c r="E25" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1394,7 +1398,9 @@
         <v>4699403</v>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
       <c r="J25" t="n">
         <v>29</v>
       </c>
@@ -2432,7 +2438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2450,111 +2456,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
+          <t>260065-P708 upper wrapping tool</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8996.5508224</v>
+        <v>18840.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250367-EHY 双机器人焊接设备 第二台</t>
+          <t>250055A-G68-LCI US welding (2台老Frimo设备改超声焊接设备)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4630.221467</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260044-DF-Liuzhou,F05-CNSL,Lamination</t>
+          <t>260168-815D825D Over Head Console Flexible Robotic Automatic Assembly Line</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2640.49</v>
+        <v>4530.64177</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260117-Papa工厂E4备件</t>
+          <t>260156-卓勇NCAR RGB 工装抓手更改</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2344.03</v>
+        <v>2281.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>240245-MBEAM 520 UBL Glue spray machine</t>
+          <t>260082-F2N灯头模组自动装配线</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1200</v>
+        <v>1522.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>250293-MMA Clipping machine</t>
+          <t>240256-灯头线 JH-C灯头模组自动生产线</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1142.52</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>260065-P708 upper wrapping tool</t>
+          <t>260008-化妆镜A-SUV工装</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1055.232</v>
+        <v>704.1688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>260050-Click Rim方向盘热压包覆</t>
+          <t>250055-BMW,G68 LCI-IP,US Welding</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>730.0884956</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>260085-780B Auto Spray</t>
+          <t>240079-W520-IP CUN lamination tool</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>337.4344828</v>
+        <v>422.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>260079-780 Flaming Process</t>
+          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>235.4</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>260116-X90DP双组分喷胶设备 第一台</t>
+          <t>240245-MBEAM 520 UBL Glue spray machine</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57.54447293</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13">
@@ -2564,7 +2570,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.5</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>260129-金桥E2LB-2-IP自动挂架</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>150.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>260077-P780 2050 单工位压机</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>260110-Scara 无序抓取</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>40.55172414</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>260050-Click Rim方向盘热压包覆</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>260115-X90DP双组分喷胶设备 第二台</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>250187-MX11门盖包覆设备A</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>13.88</v>
       </c>
     </row>
   </sheetData>
@@ -2578,7 +2644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2596,31 +2662,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>高一恒</t>
+          <t>金宇龙</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15948.67</v>
+        <v>18840.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>韦少官</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11933.47212733</v>
+        <v>4530.64177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>刘璟华</t>
+          <t>黄圣/周理文</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5394.349376</v>
+        <v>2281.67</v>
       </c>
     </row>
     <row r="5">
@@ -2630,67 +2696,97 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4804.4688</v>
+        <v>1058.1688</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>王万芳</t>
+          <t>黄圣</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3685.80531</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>陈志彬</t>
+          <t>黄东方</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1200</v>
+        <v>422.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>长江</t>
+          <t>刘璟华</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1142.52</v>
+        <v>356.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>王晓宇,王万芳</t>
+          <t>陈志彬</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>196.38</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>郝秀霞</t>
+          <t>唐明明</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>195.67</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>唐明明</t>
+          <t>胡超</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.5</v>
+        <v>172.83</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>孙一超</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>40.55172414</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王中心</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>黄琳健</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13.88</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1420,8 +1420,12 @@
           <t>CW25</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>4467.99</v>
+      </c>
+      <c r="D26" t="n">
+        <v>133502.74</v>
+      </c>
       <c r="E26" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1432,7 +1436,9 @@
         <v>4917436</v>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
       <c r="J26" t="n">
         <v>28</v>
       </c>
@@ -2438,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,181 +2462,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>260065-P708 upper wrapping tool</t>
+          <t>260160-G60 LCI IP焊接项目-US改HS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18840.69</v>
+        <v>19684.371</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>250055A-G68-LCI US welding (2台老Frimo设备改超声焊接设备)</t>
+          <t>260162-G60 LCI IP焊接项目- stage RHD 胎膜1副</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7450</v>
+        <v>2731.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260168-815D825D Over Head Console Flexible Robotic Automatic Assembly Line</t>
+          <t>260147-G90 手工包覆工装-Spacer</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4530.64177</v>
+        <v>2109.15816976</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260156-卓勇NCAR RGB 工装抓手更改</t>
+          <t>260165-G60 LCI IP 焊接-CS step 1 焊接胎具-RHD</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2281.67</v>
+        <v>1476.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>260082-F2N灯头模组自动装配线</t>
+          <t>260168-815D825D Over Head Console Flexible Robotic Automatic Assembly Line</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1522.12</v>
+        <v>1283.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>240256-灯头线 JH-C灯头模组自动生产线</t>
+          <t>250275-W530 IP CUN lamination tool</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1200</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>260008-化妆镜A-SUV工装</t>
+          <t>260082-F2N灯头模组自动装配线</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>704.1688</v>
+        <v>724.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>250055-BMW,G68 LCI-IP,US Welding</t>
+          <t>260161-G60 LCI IP焊接项目- stage LHD 胎膜1副</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>458.08</v>
+        <v>705.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>240079-W520-IP CUN lamination tool</t>
+          <t>260166-G60 LCI IP 焊接-CS step 2 焊接胎具-LHD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>422.56</v>
+        <v>450.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
+          <t>260079-780 Flaming Process</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>354</v>
+        <v>377.0942858</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>240245-MBEAM 520 UBL Glue spray machine</t>
+          <t>260156-卓勇NCAR RGB 工装抓手更改</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>229</v>
+        <v>328.7092</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>260135-smartmi,KUNLUN-light,welding.260135.M</t>
+          <t>250739-</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>260129-金桥E2LB-2-IP自动挂架</t>
+          <t>260135-smartmi,KUNLUN-light,welding.260135.M</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>150.15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>260077-P780 2050 单工位压机</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>260110-Scara 无序抓取</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>40.55172414</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>260050-Click Rim方向盘热压包覆</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>260115-X90DP双组分喷胶设备 第二台</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>22.68</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>250187-MX11门盖包覆设备A</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>13.88</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2644,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2662,31 +2618,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>金宇龙</t>
+          <t>郝秀霞</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18840.69</v>
+        <v>14147.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>韦少官</t>
+          <t>闵宏恩</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4530.64177</v>
+        <v>2109.15816976</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>黄圣/周理文</t>
+          <t>黄定辉</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2281.67</v>
+        <v>1283.09</v>
       </c>
     </row>
     <row r="5">
@@ -2696,97 +2652,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1058.1688</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>黄圣</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>458.08</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>黄东方</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>422.56</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>刘璟华</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>356.24</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>陈志彬</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>唐明明</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>胡超</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>172.83</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>孙一超</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>40.55172414</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>王中心</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>黄琳健</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>13.88</v>
+        <v>328.7092</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1458,8 +1458,12 @@
           <t>CW26</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>17887.41</v>
+      </c>
+      <c r="D27" t="n">
+        <v>19419.21</v>
+      </c>
       <c r="E27" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1470,7 +1474,9 @@
         <v>5166224</v>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
       <c r="J27" t="n">
         <v>27</v>
       </c>
@@ -2444,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2462,71 +2468,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>260160-G60 LCI IP焊接项目-US改HS</t>
+          <t>260171-L97 DAB门盖包覆胎模</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19684.371</v>
+        <v>12063.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>260162-G60 LCI IP焊接项目- stage RHD 胎膜1副</t>
+          <t>260093-水性辊胶设备+EOL视觉检测（K321&amp;P166）第一台</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2731.64</v>
+        <v>5904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260147-G90 手工包覆工装-Spacer</t>
+          <t>250371-北京V530 焊接模具OP1&amp;换模车</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2109.15816976</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260165-G60 LCI IP 焊接-CS step 1 焊接胎具-RHD</t>
+          <t>260128-E2LB-2 IP上盖板热压胎模</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1476.43</v>
+        <v>1622.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>260168-815D825D Over Head Console Flexible Robotic Automatic Assembly Line</t>
+          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1283.09</v>
+        <v>1400.9113274</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>250275-W530 IP CUN lamination tool</t>
+          <t>260168-815D825D Over Head Console Flexible Robotic Automatic Assembly Line</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>960</v>
+        <v>1283.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>260082-F2N灯头模组自动装配线</t>
+          <t>260135-smartmi,KUNLUN-light,welding.260135.M</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>724.16</v>
+        <v>1134.96</v>
       </c>
     </row>
     <row r="9">
@@ -2536,57 +2542,117 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>705.28</v>
+        <v>578.3943181999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>260166-G60 LCI IP 焊接-CS step 2 焊接胎具-LHD</t>
+          <t>260117-Papa工厂E4备件</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>450.23</v>
+        <v>565.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>260079-780 Flaming Process</t>
+          <t>260156-卓勇NCAR RGB 工装抓手更改</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>377.0942858</v>
+        <v>536.4100000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>260156-卓勇NCAR RGB 工装抓手更改</t>
+          <t>260082-F2N灯头模组自动装配线</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>328.7092</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>250739-</t>
+          <t>250055-BMW,G68 LCI-IP,US Welding</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>144</v>
+        <v>282.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>260135-smartmi,KUNLUN-light,welding.260135.M</t>
+          <t>260138-E68 DP1200小压机</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>274.36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>260164-G60 LCI IP 焊接-CS step 1 焊接胎具-LHD</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>274.21766958</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>260169-宁波辊胶设备</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>203.24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>260159-临港辊胶设备</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>172.24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>260166-G60 LCI IP 焊接-CS step 2 焊接胎具-LHD</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>167.36234849</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>230211-BR223 DP FOST Press and edge-folding tool</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>260148-G90 手工包覆工装-AB面</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>51.6</v>
       </c>
     </row>
   </sheetData>
@@ -2600,7 +2666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2618,21 +2684,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>郝秀霞</t>
+          <t>黄东方</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14147.26</v>
+        <v>11610.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>闵宏恩</t>
+          <t>赵鹏</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2109.15816976</v>
+        <v>1622.97</v>
       </c>
     </row>
     <row r="4">
@@ -2642,17 +2708,87 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1283.09</v>
+        <v>1379.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>王晓宇,王万芳</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>921.4513274</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>徐义星</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>328.7092</v>
+      <c r="B6" t="n">
+        <v>889.21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>陈洁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>849.28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>唐明明</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>614.96</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>高一恒</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>578.3943181999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>刘璟华</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>441.58001807</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>罗浩</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>周光辉</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1496,8 +1496,12 @@
           <t>CW27</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>23278.9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>49410.11</v>
+      </c>
       <c r="E28" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1508,7 +1512,9 @@
         <v>5491372</v>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
       <c r="J28" t="n">
         <v>26</v>
       </c>
@@ -2450,7 +2456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2468,191 +2474,171 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>260171-L97 DAB门盖包覆胎模</t>
+          <t>250055-BMW,G68 LCI-IP,US Welding</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12063.42</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>260093-水性辊胶设备+EOL视觉检测（K321&amp;P166）第一台</t>
+          <t>260103-BYD,Glue,260103</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5904</v>
+        <v>3346.558</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>250371-北京V530 焊接模具OP1&amp;换模车</t>
+          <t>260169-宁波辊胶设备</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3600</v>
+        <v>3346.558</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260128-E2LB-2 IP上盖板热压胎模</t>
+          <t>260159-临港辊胶设备</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1622.97</v>
+        <v>3346.558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
+          <t>260117-Papa工厂E4备件</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1400.9113274</v>
+        <v>943.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>260168-815D825D Over Head Console Flexible Robotic Automatic Assembly Line</t>
+          <t>260160-G60 LCI IP焊接项目-US改HS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1283.09</v>
+        <v>936.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>260135-smartmi,KUNLUN-light,welding.260135.M</t>
+          <t>250275-W530 IP CUN lamination tool</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1134.96</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>260161-G60 LCI IP焊接项目- stage LHD 胎膜1副</t>
+          <t>260085-780B Auto Spray</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>578.3943181999999</v>
+        <v>448.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>260117-Papa工厂E4备件</t>
+          <t>260140-C673门板自动贴海绵 （单机器人双工位）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>565.76</v>
+        <v>270.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>260156-卓勇NCAR RGB 工装抓手更改</t>
+          <t>260053-V530 地图袋包边模具后门</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>536.4100000000001</v>
+        <v>224.53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>260082-F2N灯头模组自动装配线</t>
+          <t>260052-V530 地图袋包边模具前门</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>392</v>
+        <v>224.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>250055-BMW,G68 LCI-IP,US Welding</t>
+          <t>260162-G60 LCI IP焊接项目- stage RHD 胎膜1副</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>282.96</v>
+        <v>162.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>260138-E68 DP1200小压机</t>
+          <t>260129-金桥E2LB-2-IP自动挂架</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>274.36</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>260164-G60 LCI IP 焊接-CS step 1 焊接胎具-LHD</t>
+          <t>260050-Click Rim方向盘热压包覆</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>274.21766958</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>260169-宁波辊胶设备</t>
+          <t>260167-G60 LCI IP 焊接-CS step 2 焊接胎具-RHD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>203.24</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>260159-临港辊胶设备</t>
+          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>172.24</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>260166-G60 LCI IP 焊接-CS step 2 焊接胎具-LHD</t>
+          <t>260082-F2N灯头模组自动装配线</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>167.36234849</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>230211-BR223 DP FOST Press and edge-folding tool</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>260148-G90 手工包覆工装-AB面</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>51.6</v>
+        <v>18.57</v>
       </c>
     </row>
   </sheetData>
@@ -2666,7 +2652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2684,111 +2670,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>黄东方</t>
+          <t>周华盛</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11610.22</v>
+        <v>48495.53000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>赵鹏</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1622.97</v>
+        <v>10039.674</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>黄定辉</t>
+          <t>高一恒</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1379.79</v>
+        <v>605.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>王晓宇,王万芳</t>
+          <t>陈志斌</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>921.4513274</v>
+        <v>270.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>徐义星</t>
+          <t>刘璟华</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>889.21</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>张雷</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>849.28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>唐明明</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>614.96</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>高一恒</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>578.3943181999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>刘璟华</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>441.58001807</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>罗浩</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>周光辉</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>31</v>
+        <v>22.71</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1534,8 +1534,12 @@
           <t>CW28</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>2055.94</v>
+      </c>
+      <c r="D29" t="n">
+        <v>40440.52</v>
+      </c>
       <c r="E29" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1546,7 +1550,9 @@
         <v>5687141</v>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
       <c r="J29" t="n">
         <v>25</v>
       </c>
@@ -2456,7 +2462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2474,171 +2480,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>250055-BMW,G68 LCI-IP,US Welding</t>
+          <t>260187-EIC 2S 发泡模架改压机</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7450</v>
+        <v>11975.526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>260103-BYD,Glue,260103</t>
+          <t>260186-长沙-CA01-发泡模架改压机</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3346.558</v>
+        <v>11849.612</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260169-宁波辊胶设备</t>
+          <t>260082-F2N灯头模组自动装配线</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3346.558</v>
+        <v>757.7557724000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260159-临港辊胶设备</t>
+          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3346.558</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>260117-Papa工厂E4备件</t>
+          <t>260011-EHX IP 自动装备设备</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>943.55</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>260160-G60 LCI IP焊接项目-US改HS</t>
+          <t>250287-A15(X1L) 总成检测设备</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>936.27</v>
+        <v>229.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>250275-W530 IP CUN lamination tool</t>
+          <t>260161-G60 LCI IP焊接项目- stage LHD 胎膜1副</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>600</v>
+        <v>211.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>260085-780B Auto Spray</t>
+          <t>260091-MR&amp;ST 水性辊胶机</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>448.96</v>
+        <v>155.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>260140-C673门板自动贴海绵 （单机器人双工位）</t>
+          <t>250344-VW311-6水性辊胶机</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>270.74</v>
+        <v>155.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>260053-V530 地图袋包边模具后门</t>
+          <t>260162-G60 LCI IP焊接项目- stage RHD 胎膜1副</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>224.53</v>
+        <v>99.77000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>260052-V530 地图袋包边模具前门</t>
+          <t>260077-P780 2050 单工位压机</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>224.53</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>260162-G60 LCI IP焊接项目- stage RHD 胎膜1副</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>162.16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>260129-金桥E2LB-2-IP自动挂架</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>260050-Click Rim方向盘热压包覆</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>45.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>260167-G60 LCI IP 焊接-CS step 2 焊接胎具-RHD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>32.62</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>22.71</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>260082-F2N灯头模组自动装配线</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>18.57</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -2670,61 +2616,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>周华盛</t>
+          <t>苏楠</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48495.53000000001</v>
+        <v>23825.138</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>高一恒</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10039.674</v>
+        <v>310.9400000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>高一恒</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>605.49</v>
+        <v>272.0778862</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>陈志斌</t>
+          <t>唐明明</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>270.74</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>刘璟华</t>
+          <t>顾天涯</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.62</v>
+        <v>229.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>张雷</t>
+          <t>闻先海</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.71</v>
+        <v>142.4</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/库存数据/本周库存统计.xlsx
+++ b/yanfeng/库存数据/本周库存统计.xlsx
@@ -1572,8 +1572,12 @@
           <t>CW29</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>7397.81</v>
+      </c>
+      <c r="D30" t="n">
+        <v>144858.54</v>
+      </c>
       <c r="E30" t="n">
         <v>923580.8730200001</v>
       </c>
@@ -1584,7 +1588,9 @@
         <v>5771380</v>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>28487.06</v>
+      </c>
       <c r="J30" t="n">
         <v>24</v>
       </c>
@@ -2462,7 +2468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2480,111 +2486,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>260187-EIC 2S 发泡模架改压机</t>
+          <t>260183-Tesla HLD 4038 嵌饰板2050压机改造</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11975.526</v>
+        <v>78643.6350488</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>260186-长沙-CA01-发泡模架改压机</t>
+          <t>260184-Tesla HLD 嵌饰板包覆复制模前门</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11849.612</v>
+        <v>16877.03414518</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260082-F2N灯头模组自动装配线</t>
+          <t>260185-Tesla HLD 嵌饰板包覆复制模后门</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>757.7557724000001</v>
+        <v>14980.23080852</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>250379-SERES Motors,F3_Seat rail,Assy</t>
+          <t>260168-815D825D Over Head Console Flexible Robotic Automatic Assembly Line</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>390</v>
+        <v>6439.07585187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>260011-EHX IP 自动装备设备</t>
+          <t>260193-EHX CNSL左右护板总成2050单工位压机 第二台</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>4700.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>250287-A15(X1L) 总成检测设备</t>
+          <t>250262-W530 IP CUN  welding tool</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>229.57</v>
+        <v>913.5899999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>260161-G60 LCI IP焊接项目- stage LHD 胎膜1副</t>
+          <t>240211-MBEAM 520 UBL lamination tool  1T #2- S项</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>211.17</v>
+        <v>682.601</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>260091-MR&amp;ST 水性辊胶机</t>
+          <t>250275-W530 IP CUN lamination tool</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155.99</v>
+        <v>371.681</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>250344-VW311-6水性辊胶机</t>
+          <t>260160-G60 LCI IP焊接项目-US改HS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155.99</v>
+        <v>263.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>260162-G60 LCI IP焊接项目- stage RHD 胎膜1副</t>
+          <t>260103-BYD,Glue,260103</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99.77000000000001</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>260077-P780 2050 单工位压机</t>
+          <t>260192-常州辊胶设备</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.5</v>
+        <v>190.74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>230211-BR223 DP FOST Press and edge-folding tool</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>96.450745488</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>260262-</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>85.428</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>260138-E68 DP1200小压机</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>78.4686</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>260128-E2LB-2 IP上盖板热压胎模</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>42.37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>260176-AS5PM IP右舵激光弱化胎膜</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>29.87</v>
       </c>
     </row>
   </sheetData>
@@ -2598,7 +2654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2616,61 +2672,99 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>苏楠</t>
+          <t>徐义星</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23825.138</v>
+        <v>78521.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>高一恒</t>
+          <t>樊爱强</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>310.9400000000001</v>
+        <v>27920.86136024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>报废</t>
+          <t>徐天丰</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>272.0778862</v>
+        <v>5995.2488</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>唐明明</t>
+          <t>黄琳健</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>270</v>
+        <v>4700.34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>顾天涯</t>
+          <t>丁宝强</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>229.57</v>
+        <v>2620.49889656</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>闻先海</t>
+          <t>报废</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142.4</v>
+        <v>1891.757543058</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>郝秀霞</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>263.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>190.74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>260138</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78.4686</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>阚城奔</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>42.37</v>
       </c>
     </row>
   </sheetData>
@@ -2684,7 +2778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2699,6 +2793,46 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>250337-EHV DP 自动包覆胎具（后左热压）</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>23575.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>250383-F2N DAB Lamination胎模,1T</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3093.52</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>260116-Huawei Anhui,X90-DP,260116</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1427.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>260077-</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>391.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
